--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487473_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487473_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.9136</v>
+        <v>6.8322</v>
       </c>
       <c r="E2" t="n">
-        <v>3.7084</v>
+        <v>4.2795</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2052</v>
+        <v>2.5527</v>
       </c>
       <c r="G2" t="n">
         <v>3.6049</v>
@@ -610,13 +610,13 @@
         <v>3.1336</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.6498</v>
+        <v>-0.7312</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4288</v>
+        <v>0.1423</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.221</v>
+        <v>-0.8735000000000001</v>
       </c>
       <c r="V2" t="n">
         <v>1.2166</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.8262</v>
+        <v>6.7877</v>
       </c>
       <c r="E3" t="n">
-        <v>5.068</v>
+        <v>5.682</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7583</v>
+        <v>1.1058</v>
       </c>
       <c r="G3" t="n">
         <v>7.4773</v>
@@ -688,13 +688,13 @@
         <v>2.1543</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7893</v>
+        <v>0.1722</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2506</v>
+        <v>0.3635</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5387999999999999</v>
+        <v>-0.1913</v>
       </c>
       <c r="V3" t="n">
         <v>-0.6659</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.2889</v>
+        <v>5.098</v>
       </c>
       <c r="E4" t="n">
-        <v>3.911</v>
+        <v>3.3993</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3779</v>
+        <v>1.6987</v>
       </c>
       <c r="G4" t="n">
         <v>0.8123</v>
@@ -766,13 +766,13 @@
         <v>1.5668</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5573</v>
+        <v>0.3664</v>
       </c>
       <c r="T4" t="n">
-        <v>1.4109</v>
+        <v>0.8993</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.8536</v>
+        <v>-0.5328000000000001</v>
       </c>
       <c r="V4" t="n">
         <v>2.5484</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.2027</v>
+        <v>4.1851</v>
       </c>
       <c r="E5" t="n">
-        <v>3.6943</v>
+        <v>3.4896</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5084</v>
+        <v>0.6955</v>
       </c>
       <c r="G5" t="n">
         <v>4.6738</v>
@@ -844,13 +844,13 @@
         <v>0.3917</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0589</v>
+        <v>0.0413</v>
       </c>
       <c r="T5" t="n">
-        <v>0.207</v>
+        <v>0.0023</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1482</v>
+        <v>0.039</v>
       </c>
       <c r="V5" t="n">
         <v>0.0576</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. GONZALEZ CORDERO</t>
+          <t>F. SALVADORES ALVAREZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.2266</v>
+        <v>1.752</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9603</v>
+        <v>3.6836</v>
       </c>
       <c r="F6" t="n">
-        <v>3.1869</v>
+        <v>-1.9315</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5118</v>
+        <v>5.846</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2008</v>
+        <v>1.6428</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7126</v>
+        <v>4.2032</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5681</v>
+        <v>5.8356</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4064</v>
+        <v>2.5927</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1617</v>
+        <v>3.2428</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0563</v>
+        <v>0.0104</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6073</v>
+        <v>-0.9499</v>
       </c>
       <c r="O6" t="n">
-        <v>0.551</v>
+        <v>0.9603</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.3502</v>
+        <v>-1.3709</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.1128</v>
+        <v>-2.1543</v>
       </c>
       <c r="R6" t="n">
-        <v>1.7626</v>
+        <v>0.7834</v>
       </c>
       <c r="S6" t="n">
-        <v>3.5143</v>
+        <v>-0.0144</v>
       </c>
       <c r="T6" t="n">
-        <v>2.0338</v>
+        <v>0.0023</v>
       </c>
       <c r="U6" t="n">
-        <v>1.4805</v>
+        <v>-0.0168</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5507</v>
+        <v>-2.7086</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5507</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-2.7086</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F. SALVADORES ALVAREZ</t>
+          <t>A. GONZALEZ CORDERO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.0102</v>
+        <v>-0.0439</v>
       </c>
       <c r="E7" t="n">
-        <v>3.8882</v>
+        <v>-2.1883</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.8781</v>
+        <v>2.1444</v>
       </c>
       <c r="G7" t="n">
-        <v>5.846</v>
+        <v>0.5118</v>
       </c>
       <c r="H7" t="n">
-        <v>1.6428</v>
+        <v>-0.2008</v>
       </c>
       <c r="I7" t="n">
-        <v>4.2032</v>
+        <v>0.7126</v>
       </c>
       <c r="J7" t="n">
-        <v>5.8356</v>
+        <v>0.5681</v>
       </c>
       <c r="K7" t="n">
-        <v>2.5927</v>
+        <v>0.4064</v>
       </c>
       <c r="L7" t="n">
-        <v>3.2428</v>
+        <v>0.1617</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0104</v>
+        <v>-0.0563</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9499</v>
+        <v>-0.6073</v>
       </c>
       <c r="O7" t="n">
-        <v>0.9603</v>
+        <v>0.551</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.3709</v>
+        <v>-2.3502</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.1543</v>
+        <v>-4.1128</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7834</v>
+        <v>1.7626</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2437</v>
+        <v>1.2438</v>
       </c>
       <c r="T7" t="n">
-        <v>0.207</v>
+        <v>0.8057</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0367</v>
+        <v>0.438</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.7086</v>
+        <v>0.5507</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.5507</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.7086</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0313</v>
+        <v>-0.1695</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3308</v>
+        <v>-0.2284</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2995</v>
+        <v>0.0589</v>
       </c>
       <c r="G8" t="n">
         <v>0.437</v>
@@ -1078,13 +1078,13 @@
         <v>0.7834</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1607</v>
+        <v>0.0225</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.297</v>
+        <v>-0.1947</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4577</v>
+        <v>0.2172</v>
       </c>
       <c r="V8" t="n">
         <v>-1.2166</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. CACHON VILLAMEDIANA</t>
+          <t>A. NONGO N'SALA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.1304</v>
+        <v>-1.2197</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7687</v>
+        <v>-1.573</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6383</v>
+        <v>0.3532</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7537</v>
+        <v>0.1369</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.3634</v>
+        <v>-0.707</v>
       </c>
       <c r="I9" t="n">
-        <v>2.1172</v>
+        <v>0.8439</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4756</v>
+        <v>-0.4797</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.4135</v>
+        <v>-0.6414</v>
       </c>
       <c r="L9" t="n">
-        <v>0.8891</v>
+        <v>0.1617</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2781</v>
+        <v>0.6166</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9499</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>1.228</v>
+        <v>0.6822</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.5875</v>
+        <v>0.1958</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.1543</v>
+        <v>-0.9792</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5668</v>
+        <v>1.1751</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0212</v>
+        <v>-0.6112</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.09</v>
+        <v>-0.3893</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.9312</v>
+        <v>-0.2219</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2754</v>
+        <v>-0.9412</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2754</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. NONGO N'SALA</t>
+          <t>R. CACHON VILLAMEDIANA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4036</v>
+        <v>-1.2397</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.8371</v>
+        <v>-2.1186</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4334</v>
+        <v>0.8789</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1369</v>
+        <v>0.7537</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.707</v>
+        <v>-1.3634</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8439</v>
+        <v>2.1172</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.4797</v>
+        <v>0.4756</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6414</v>
+        <v>-0.4135</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1617</v>
+        <v>0.8891</v>
       </c>
       <c r="M10" t="n">
-        <v>0.6166</v>
+        <v>0.2781</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.06560000000000001</v>
+        <v>-0.9499</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6822</v>
+        <v>1.228</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1958</v>
+        <v>-0.5875</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9792</v>
+        <v>-2.1543</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1751</v>
+        <v>1.5668</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7951</v>
+        <v>-1.1305</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6534</v>
+        <v>-0.4399</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1417</v>
+        <v>-0.6906</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.9412</v>
+        <v>-0.2754</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2166</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. PEREZ MARTIN</t>
+          <t>Y. IGLESIAS MENDEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.7581</v>
+        <v>-2.1206</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.2844</v>
+        <v>-4.7089</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5263</v>
+        <v>2.5883</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.5402</v>
+        <v>-4.6044</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.6407</v>
+        <v>-1.4409</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1005</v>
+        <v>-3.1635</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.96</v>
+        <v>-5.0929</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.373</v>
+        <v>-1.242</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5869</v>
+        <v>-3.8509</v>
       </c>
       <c r="M11" t="n">
-        <v>0.4197</v>
+        <v>0.4885</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2677</v>
+        <v>-0.199</v>
       </c>
       <c r="O11" t="n">
         <v>0.6874</v>
       </c>
       <c r="P11" t="n">
-        <v>0.3917</v>
+        <v>1.7626</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1751</v>
+        <v>-0.9792</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5668</v>
+        <v>2.7419</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4506</v>
+        <v>-0.4379</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1494</v>
+        <v>-0.0712</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3012</v>
+        <v>-0.3667</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.159</v>
+        <v>1.159</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.4344</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.159</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Y. IGLESIAS MENDEZ</t>
+          <t>R. PEREZ MARTIN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.2614</v>
+        <v>-2.6812</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.6894</v>
+        <v>-3.0204</v>
       </c>
       <c r="F12" t="n">
-        <v>2.4279</v>
+        <v>0.3392</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.6044</v>
+        <v>-1.5402</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.4409</v>
+        <v>-1.6407</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.1635</v>
+        <v>0.1005</v>
       </c>
       <c r="J12" t="n">
-        <v>-5.0929</v>
+        <v>-1.96</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.242</v>
+        <v>-1.373</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.8509</v>
+        <v>-0.5869</v>
       </c>
       <c r="M12" t="n">
-        <v>0.4885</v>
+        <v>0.4197</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.199</v>
+        <v>-0.2677</v>
       </c>
       <c r="O12" t="n">
         <v>0.6874</v>
       </c>
       <c r="P12" t="n">
-        <v>1.7626</v>
+        <v>0.3917</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9792</v>
+        <v>-1.1751</v>
       </c>
       <c r="R12" t="n">
-        <v>2.7419</v>
+        <v>1.5668</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.5787</v>
+        <v>-0.3736</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0516</v>
+        <v>0.1147</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5271</v>
+        <v>-0.4883</v>
       </c>
       <c r="V12" t="n">
-        <v>1.159</v>
+        <v>-1.159</v>
       </c>
       <c r="W12" t="n">
-        <v>1.4344</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.2754</v>
+        <v>-1.159</v>
       </c>
     </row>
     <row r="13">
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>16.8834</v>
+        <v>17.1804</v>
       </c>
       <c r="E13" t="n">
-        <v>6.399199999999998</v>
+        <v>6.696399999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>10.484</v>
+        <v>10.4841</v>
       </c>
       <c r="G13" t="n">
-        <v>18.10910000000001</v>
+        <v>18.1091</v>
       </c>
       <c r="H13" t="n">
         <v>-6.114</v>
@@ -1453,13 +1453,13 @@
         <v>2.4995</v>
       </c>
       <c r="N13" t="n">
-        <v>-5.739399999999999</v>
+        <v>-5.7394</v>
       </c>
       <c r="O13" t="n">
         <v>8.2386</v>
       </c>
       <c r="P13" t="n">
-        <v>1.958499999999999</v>
+        <v>1.9585</v>
       </c>
       <c r="Q13" t="n">
         <v>-15.6676</v>
@@ -1468,13 +1468,13 @@
         <v>17.6264</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.7498</v>
+        <v>-1.4526</v>
       </c>
       <c r="T13" t="n">
-        <v>0.9379</v>
+        <v>1.235</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.6879</v>
+        <v>-2.6877</v>
       </c>
       <c r="V13" t="n">
         <v>-1.4344</v>
@@ -1483,7 +1483,7 @@
         <v>5.5198</v>
       </c>
       <c r="X13" t="n">
-        <v>-6.954199999999999</v>
+        <v>-6.9542</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.4932</v>
+        <v>1.4886</v>
       </c>
       <c r="E14" t="n">
-        <v>4.6534</v>
+        <v>1.3787</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.1602</v>
+        <v>0.1099</v>
       </c>
       <c r="G14" t="n">
         <v>-0.7249</v>
@@ -1546,13 +1546,13 @@
         <v>2.1543</v>
       </c>
       <c r="S14" t="n">
-        <v>4.9</v>
+        <v>1.8954</v>
       </c>
       <c r="T14" t="n">
-        <v>5.0885</v>
+        <v>1.8138</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1885</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>1.1014</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3539</v>
+        <v>0.9992</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.3041</v>
+        <v>0.2076</v>
       </c>
       <c r="F15" t="n">
-        <v>0.658</v>
+        <v>0.7916</v>
       </c>
       <c r="G15" t="n">
         <v>-0.204</v>
@@ -1624,13 +1624,13 @@
         <v>1.3709</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8131</v>
+        <v>-0.1678</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3564</v>
+        <v>0.1553</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4567</v>
+        <v>-0.323</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2433</v>
+        <v>0.7374000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5455</v>
+        <v>0.8525</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3022</v>
+        <v>-0.1151</v>
       </c>
       <c r="G16" t="n">
         <v>0.6291</v>
@@ -1702,13 +1702,13 @@
         <v>0.7834</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.1692</v>
+        <v>-0.675</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4752</v>
+        <v>-0.1682</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6939</v>
+        <v>-0.5068</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0113</v>
+        <v>0.0159</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3767</v>
+        <v>-0.4791</v>
       </c>
       <c r="F17" t="n">
-        <v>0.388</v>
+        <v>0.4949</v>
       </c>
       <c r="G17" t="n">
         <v>-0.0384</v>
@@ -1780,13 +1780,13 @@
         <v>0.7834</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0299</v>
+        <v>-0.0253</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5810999999999999</v>
+        <v>0.4787</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.611</v>
+        <v>-0.504</v>
       </c>
       <c r="V17" t="n">
         <v>0.2754</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L. PORTILLA QUEIRO</t>
+          <t>N. LAGARES COUCE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5898</v>
+        <v>-0.7004</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2776</v>
+        <v>0.6034</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.8673999999999999</v>
+        <v>-1.3038</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2037</v>
+        <v>-0.7092000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>4.0195</v>
+        <v>0.3212</v>
       </c>
       <c r="I18" t="n">
-        <v>-4.2232</v>
+        <v>-1.0304</v>
       </c>
       <c r="J18" t="n">
-        <v>2.7296</v>
+        <v>1.3668</v>
       </c>
       <c r="K18" t="n">
-        <v>4.0132</v>
+        <v>0.7962</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.2836</v>
+        <v>0.5706</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.9333</v>
+        <v>-2.076</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0062</v>
+        <v>-0.475</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.9395</v>
+        <v>-1.601</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.3917</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.9377</v>
+        <v>-0.9792</v>
       </c>
       <c r="R18" t="n">
-        <v>2.546</v>
+        <v>0.9792</v>
       </c>
       <c r="S18" t="n">
-        <v>1.8881</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>0.8763</v>
+        <v>0.2158</v>
       </c>
       <c r="U18" t="n">
-        <v>1.0118</v>
+        <v>-0.207</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.8825</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.3905</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.492</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. CISSOKO</t>
+          <t>J. GONZALEZ VAZQUEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9226</v>
+        <v>-0.978</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1434</v>
+        <v>-0.9608</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.066</v>
+        <v>-0.0171</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.9321</v>
+        <v>-2.5988</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7649</v>
+        <v>-0.7145</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.6971</v>
+        <v>-1.8843</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5304</v>
+        <v>-1.2624</v>
       </c>
       <c r="K19" t="n">
-        <v>0.49</v>
+        <v>-0.5802</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0404</v>
+        <v>-0.6822</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.4625</v>
+        <v>-1.3364</v>
       </c>
       <c r="N19" t="n">
-        <v>0.275</v>
+        <v>-0.1344</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.7375</v>
+        <v>-1.2021</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1751</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1751</v>
+        <v>0.5875</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3264</v>
+        <v>-0.1453</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.387</v>
+        <v>-0.2111</v>
       </c>
       <c r="U19" t="n">
-        <v>0.7134</v>
+        <v>0.0659</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.492</v>
+        <v>2.1578</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.492</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.492</v>
+        <v>0.6659</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. GONZALEZ VAZQUEZ</t>
+          <t>M. CISSOKO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2895</v>
+        <v>-1.1098</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1655</v>
+        <v>0.1434</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1241</v>
+        <v>-1.2531</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.5988</v>
+        <v>-0.9321</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.7145</v>
+        <v>0.7649</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.8843</v>
+        <v>-1.6971</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.2624</v>
+        <v>0.5304</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.5802</v>
+        <v>0.49</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6822</v>
+        <v>0.0404</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.3364</v>
+        <v>-1.4625</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1344</v>
+        <v>0.275</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.2021</v>
+        <v>-1.7375</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.3917</v>
+        <v>1.1751</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.5875</v>
+        <v>1.1751</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4569</v>
+        <v>0.1392</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4158</v>
+        <v>-0.387</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.041</v>
+        <v>0.5262</v>
       </c>
       <c r="V20" t="n">
-        <v>2.1578</v>
+        <v>-1.492</v>
       </c>
       <c r="W20" t="n">
-        <v>1.492</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.6659</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5009</v>
+        <v>-1.3184</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.603</v>
+        <v>-1.5007</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1021</v>
+        <v>0.1823</v>
       </c>
       <c r="G21" t="n">
         <v>-0.4362</v>
@@ -2092,13 +2092,13 @@
         <v>0.3917</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2018</v>
+        <v>-0.0193</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0176</v>
+        <v>0.12</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2194</v>
+        <v>-0.1392</v>
       </c>
       <c r="V21" t="n">
         <v>-0.2754</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>N. LAGARES COUCE</t>
+          <t>L. PORTILLA QUEIRO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.5577</v>
+        <v>-1.4332</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.0106</v>
+        <v>0.073</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.5471</v>
+        <v>-1.5062</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.7092000000000001</v>
+        <v>-0.2037</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3212</v>
+        <v>4.0195</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.0304</v>
+        <v>-4.2232</v>
       </c>
       <c r="J22" t="n">
-        <v>1.3668</v>
+        <v>2.7296</v>
       </c>
       <c r="K22" t="n">
-        <v>0.7962</v>
+        <v>4.0132</v>
       </c>
       <c r="L22" t="n">
-        <v>0.5706</v>
+        <v>-1.2836</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.076</v>
+        <v>-2.9333</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.475</v>
+        <v>0.0062</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.601</v>
+        <v>-2.9395</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9792</v>
+        <v>-2.9377</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9792</v>
+        <v>2.546</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8486</v>
+        <v>1.0447</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3982</v>
+        <v>0.6716</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4504</v>
+        <v>0.373</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-1.8825</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.3905</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. ROZAS RAMOS</t>
+          <t>J. ABELLEIRA MARTINEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.2658</v>
+        <v>-1.8861</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.2692</v>
+        <v>-2.0045</v>
       </c>
       <c r="F23" t="n">
-        <v>1.0034</v>
+        <v>0.1184</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.287</v>
+        <v>-1.9406</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.5339</v>
+        <v>2.0857</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.7531</v>
+        <v>-4.0263</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.1046</v>
+        <v>0.5167</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.7401</v>
+        <v>1.8763</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.3645</v>
+        <v>-1.3597</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.1823</v>
+        <v>-2.4573</v>
       </c>
       <c r="N23" t="n">
-        <v>0.2062</v>
+        <v>0.2094</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.3886</v>
+        <v>-2.6667</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>-2.3502</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9792</v>
+        <v>-4.8962</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9792</v>
+        <v>2.546</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6294999999999999</v>
+        <v>-0.0285</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1476</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4819</v>
+        <v>-0.0279</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.6083</v>
+        <v>2.4332</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.3329</v>
+        <v>2.3756</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.2754</v>
+        <v>0.0576</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. ABELLEIRA MARTINEZ</t>
+          <t>M. ROZAS RAMOS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.9971</v>
+        <v>-2.6087</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.9255</v>
+        <v>-3.3715</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.07149999999999999</v>
+        <v>0.7628</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.9406</v>
+        <v>-2.287</v>
       </c>
       <c r="H24" t="n">
-        <v>2.0857</v>
+        <v>-0.5339</v>
       </c>
       <c r="I24" t="n">
-        <v>-4.0263</v>
+        <v>-1.7531</v>
       </c>
       <c r="J24" t="n">
-        <v>0.5167</v>
+        <v>-2.1046</v>
       </c>
       <c r="K24" t="n">
-        <v>1.8763</v>
+        <v>-0.7401</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.3597</v>
+        <v>-1.3645</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.4573</v>
+        <v>-0.1823</v>
       </c>
       <c r="N24" t="n">
-        <v>0.2094</v>
+        <v>0.2062</v>
       </c>
       <c r="O24" t="n">
-        <v>-2.6667</v>
+        <v>-0.3886</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.3502</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>-4.8962</v>
+        <v>-0.9792</v>
       </c>
       <c r="R24" t="n">
-        <v>2.546</v>
+        <v>0.9792</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.1395</v>
+        <v>0.2866</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.9216</v>
+        <v>0.0453</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2178</v>
+        <v>0.2413</v>
       </c>
       <c r="V24" t="n">
-        <v>2.4332</v>
+        <v>-0.6083</v>
       </c>
       <c r="W24" t="n">
-        <v>2.3756</v>
+        <v>-0.3329</v>
       </c>
       <c r="X24" t="n">
-        <v>0.0576</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-10.8615</v>
+        <v>-9.4077</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.4494</v>
+        <v>-5.426</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.4121</v>
+        <v>-3.9817</v>
       </c>
       <c r="G25" t="n">
         <v>-8.6631</v>
@@ -2404,13 +2404,13 @@
         <v>1.3709</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.3355</v>
+        <v>0.1184</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.0692</v>
+        <v>-0.0459</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2662</v>
+        <v>0.1642</v>
       </c>
       <c r="V25" t="n">
         <v>-0.2754</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-16.8832</v>
+        <v>-16.2012</v>
       </c>
       <c r="E26" t="n">
-        <v>-10.4841</v>
+        <v>-10.484</v>
       </c>
       <c r="F26" t="n">
-        <v>-6.399099999999999</v>
+        <v>-5.7171</v>
       </c>
       <c r="G26" t="n">
         <v>-18.1089</v>
@@ -2455,10 +2455,10 @@
         <v>-24.2231</v>
       </c>
       <c r="J26" t="n">
-        <v>-2.4994</v>
+        <v>-2.499399999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>5.7393</v>
+        <v>5.739300000000002</v>
       </c>
       <c r="L26" t="n">
         <v>-8.238800000000001</v>
@@ -2467,7 +2467,7 @@
         <v>-15.6093</v>
       </c>
       <c r="N26" t="n">
-        <v>0.3747</v>
+        <v>0.3747000000000001</v>
       </c>
       <c r="O26" t="n">
         <v>-15.9844</v>
@@ -2482,19 +2482,19 @@
         <v>15.6676</v>
       </c>
       <c r="S26" t="n">
-        <v>1.7495</v>
+        <v>2.431899999999999</v>
       </c>
       <c r="T26" t="n">
         <v>2.6877</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.9377999999999999</v>
+        <v>-0.2557000000000003</v>
       </c>
       <c r="V26" t="n">
         <v>1.4342</v>
       </c>
       <c r="W26" t="n">
-        <v>6.9542</v>
+        <v>6.954199999999998</v>
       </c>
       <c r="X26" t="n">
         <v>-5.5199</v>
